--- a/residentsfulllist.xlsx
+++ b/residentsfulllist.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F242"/>
+  <dimension ref="A1:F244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="7"/>
@@ -624,22 +624,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Adebambo</t>
+          <t>Adaigbe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dele</t>
+          <t>Success</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>No 20 Sam Ogegbo Road</t>
+          <t>7 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2349153483352</t>
+          <t>2348164289106</t>
         </is>
       </c>
     </row>
@@ -649,27 +649,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Adedoyin</t>
+          <t>Adebambo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ayokunnumi</t>
+          <t>Dele</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23B Jibewa Shomorin Close</t>
+          <t>No 20 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2347018028053</t>
+          <t>2349153483352</t>
         </is>
       </c>
     </row>
@@ -679,27 +679,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Adegbite</t>
+          <t>Adedoyin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Ayokunnumi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2 Sam Ogegbo Road</t>
+          <t>23B Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2347059357158</t>
+          <t>2347018028053</t>
         </is>
       </c>
     </row>
@@ -714,22 +714,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Adegboye</t>
+          <t>Adegbite</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adeniyi</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14 Jibewa Shomorin Close</t>
+          <t>2 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2348060227640</t>
+          <t>2347059357158</t>
         </is>
       </c>
     </row>
@@ -894,22 +894,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ademoye </t>
+          <t>Adeniji</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Temitayo</t>
+          <t>Bayo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4 Martins Street</t>
+          <t>15 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2348067136212</t>
+          <t>2348118062235</t>
         </is>
       </c>
     </row>
@@ -924,22 +924,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Adeniji</t>
+          <t>Adeoti</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bayo</t>
+          <t>David</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15 Jibewa Shomorin Close</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2348118062235</t>
+          <t>2349038817804</t>
         </is>
       </c>
     </row>
@@ -954,22 +954,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Adeniyi</t>
+          <t>Adepitan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solomon </t>
+          <t>Femi</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4 Martins Street</t>
+          <t>18 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2348067155887</t>
+          <t>2348036397591</t>
         </is>
       </c>
     </row>
@@ -984,22 +984,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Adepitan</t>
+          <t>Adepoju</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Femi</t>
+          <t>Adeola</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18 Sam Ogegbo Road</t>
+          <t xml:space="preserve">7 Jibewa Shomorin Close	</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2348036397591</t>
+          <t>2347039229295</t>
         </is>
       </c>
     </row>
@@ -1044,20 +1044,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Adetayo</t>
+          <t>Adetokunboh</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>na</t>
+          <t xml:space="preserve"> A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2 Jibewa Shomorin Close</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>7 Martins Street</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1070,22 +1074,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Adetokunboh</t>
+          <t>Adetunji</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A</t>
+          <t>Adetayo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7 Martins Street</t>
+          <t>2 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348163988888</t>
         </is>
       </c>
     </row>
@@ -1100,22 +1104,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Adetunji</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Olayinka</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6 Jibewa Shomorin Close</t>
+          <t>23A Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2348163988888</t>
+          <t>2348039691036</t>
         </is>
       </c>
     </row>
@@ -1125,27 +1129,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Pastor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Adigun</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Olayinka</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23A Jibewa Shomorin Close</t>
+          <t>22 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2348039691036</t>
+          <t>2348033215244</t>
         </is>
       </c>
     </row>
@@ -1155,27 +1159,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pastor</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Adigun</t>
+          <t>Adun</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Ayodele</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22 Jibewa Shomorin Close</t>
+          <t>13 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2348033215244</t>
+          <t>2347065589088</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1189,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1205,7 +1209,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2347065589088</t>
+          <t>2348055060581</t>
         </is>
       </c>
     </row>
@@ -1220,22 +1224,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Adun</t>
+          <t>Afolabi</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ayodele</t>
+          <t>Olasumbo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13 Jibewa Shomorin Close</t>
+          <t>6 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2348055060581</t>
+          <t>2348095056885</t>
         </is>
       </c>
     </row>
@@ -1245,27 +1249,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Afolabi</t>
+          <t>Afunnize</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6 Jibewa Shomorin Close</t>
+          <t>4 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2348095056885</t>
+          <t>2348023330391</t>
         </is>
       </c>
     </row>
@@ -1280,22 +1284,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Afunnize</t>
+          <t>Ajibuwa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Gbenga</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4 Jibewa Shomorin Close</t>
+          <t>25 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2348023330391</t>
+          <t>2347036478079</t>
         </is>
       </c>
     </row>
@@ -1310,22 +1314,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ajibuwa</t>
+          <t>Ajila</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Gbenga</t>
+          <t>Ayo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>25 Jibewa Shomorin Close</t>
+          <t>15 Victorious Avenue</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2347036478079</t>
+          <t>2348034828772</t>
         </is>
       </c>
     </row>
@@ -1340,22 +1344,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ajila</t>
+          <t>Ajisafe</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ayo</t>
+          <t>Kayode</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15 Victorious Avenue</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2348034828772</t>
+          <t>2348139987919</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1439,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
+          <t>Bukky</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1445,7 +1449,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2348062661632</t>
+          <t>2348088396446</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1469,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bukky</t>
+          <t>Ibrahim</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1475,7 +1479,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2348088396446</t>
+          <t>2348062661632</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1759,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1765,7 +1769,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Anyakpo</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1790,7 +1794,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Anifowose A .O</t>
+          <t>Anifowose</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2450,22 +2454,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bish</t>
+          <t>Bidemi</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bolaji</t>
+          <t>Olayemi</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>4 Martins Street</t>
+          <t>7 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2349032346583</t>
+          <t>07039229295</t>
         </is>
       </c>
     </row>
@@ -2475,27 +2479,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Blessing</t>
+          <t>Bish</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Emmem</t>
+          <t>Bolaji</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20 Sam Ogegbo Road</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2349032346583</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2519,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Uba</t>
+          <t>Emmem</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2525,7 +2529,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2347064681113</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2595,27 +2599,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dad </t>
+          <t>Comfort</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Bendel House</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>7 Olanpejo Street</t>
+          <t>20 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348067050484</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2634,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dad Yinka</t>
+          <t xml:space="preserve">Dad </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>8 Sam Ogegbo Road</t>
+          <t>7 Olanpejo Street</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2655,27 +2659,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dada</t>
+          <t>Dad Yinka</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>10 Jibewa Shomorin Close</t>
+          <t>8 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>254705913730</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2685,27 +2689,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Dada</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Paradise</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>10 Martins Street</t>
+          <t>10 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2349134413661</t>
+          <t>254705913730</t>
         </is>
       </c>
     </row>
@@ -2750,22 +2754,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Daniju</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Paradise</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>3 Olanpejo Street</t>
+          <t>10 Martins Street</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2348117717148</t>
+          <t>2349134413661</t>
         </is>
       </c>
     </row>
@@ -2780,22 +2784,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dare</t>
+          <t>Daniju</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Adeogun</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>3 Olanpejo Street</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2348062105535</t>
+          <t>2348117717148</t>
         </is>
       </c>
     </row>
@@ -2810,22 +2814,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Dare</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Adeogun</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>7 Victorious Avenue</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348062105535</t>
         </is>
       </c>
     </row>
@@ -2850,12 +2854,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>23 Sam Ogegbo Road</t>
+          <t>7 Victorious Avenue</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2349038817804</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3259,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3285,27 +3289,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fayemi</t>
+          <t>Fakorede</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Taiwo</t>
+          <t xml:space="preserve">Elizabeth </t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>3 Jibewa Shomorin Close</t>
+          <t>7 Martins Street</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2348034317485</t>
+          <t>2347065873996</t>
         </is>
       </c>
     </row>
@@ -3320,22 +3324,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Femi</t>
+          <t>Fayemi</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Akinwunmi</t>
+          <t>Taiwo</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>23A Jibewa Shomorin Close</t>
+          <t>3 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2348035651323</t>
+          <t>2348034317485</t>
         </is>
       </c>
     </row>
@@ -3345,27 +3349,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Filade</t>
+          <t>Femi</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Olumide</t>
+          <t>Akinwunmi</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>3 Jibewa Shomorin Close</t>
+          <t>23A Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2348023073320</t>
+          <t>2348035651323</t>
         </is>
       </c>
     </row>
@@ -3375,27 +3379,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Gbonegun</t>
+          <t>Filade</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Femi</t>
+          <t>Olumide</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>22 Jibewa Shomorin Close</t>
+          <t>3 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2348065016641</t>
+          <t>2348023073320</t>
         </is>
       </c>
     </row>
@@ -3410,22 +3414,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Gbonegun</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Gbenga</t>
+          <t>Femi</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>19 Sam Ogegbo Road</t>
+          <t>22 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348065016641</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3439,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3445,17 +3449,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Temitope</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>19 Sam Ogegbo Road</t>
+          <t>18 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2348033193376</t>
+          <t>16185140886</t>
         </is>
       </c>
     </row>
@@ -3475,17 +3479,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>Temitope</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>18 Jibewa Shomorin Close</t>
+          <t>19 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2348060797200</t>
+          <t>2348033193376</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3499,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3515,7 +3519,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>16185140886</t>
+          <t>2348060797200</t>
         </is>
       </c>
     </row>
@@ -3525,27 +3529,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>George</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Gbenga</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4 Martins Street</t>
+          <t>19 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2347061533148</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3555,27 +3559,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Godwin</t>
+          <t>Gift</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Nwosu</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15 Olanpejo Street</t>
+          <t>4 Martins Street</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2348030964175</t>
+          <t>2347061533148</t>
         </is>
       </c>
     </row>
@@ -3590,22 +3594,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Godwin</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Nwosu</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>15 Olanpejo Street</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348030964175</t>
         </is>
       </c>
     </row>
@@ -3620,22 +3624,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hassan</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Yinusa</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>18 Sam Ogegbo Road</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2349079864312</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3650,22 +3654,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Hassan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Ani</t>
+          <t>Yinusa</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>5 Victorious Avenue</t>
+          <t>18 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2347037603628</t>
+          <t>2349079864312</t>
         </is>
       </c>
     </row>
@@ -3680,22 +3684,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ibukun </t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Akintade</t>
+          <t>Ani</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1 Sam Ogegbo Road</t>
+          <t>5 Victorious Avenue</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2348074088887</t>
+          <t>2347037603628</t>
         </is>
       </c>
     </row>
@@ -3705,27 +3709,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ifeoma</t>
+          <t xml:space="preserve">Ibukun </t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Emeka</t>
+          <t>Akintade</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>No 3 Martins Street</t>
+          <t>1 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2349154628676</t>
+          <t>2348074088887</t>
         </is>
       </c>
     </row>
@@ -3735,27 +3739,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Igwe</t>
+          <t>Ifeoma</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ebuka</t>
+          <t>Emeka</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>5 Martins Street</t>
+          <t>No 3 Martins Street</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2348105620740</t>
+          <t>2349154628676</t>
         </is>
       </c>
     </row>
@@ -3800,22 +3804,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Igwillo</t>
+          <t>Igwe</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinton </t>
+          <t xml:space="preserve"> Ebuka</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>5 Jibewa Shomorin Close</t>
+          <t>5 Martins Street</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2348038588597</t>
+          <t>2348105620740</t>
         </is>
       </c>
     </row>
@@ -3830,22 +3834,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Iheme</t>
+          <t>Igwillo</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Ekene</t>
+          <t xml:space="preserve">Clinton </t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>17 Jibewa Shomorin Close</t>
+          <t>5 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2348035007625</t>
+          <t>2348038588597</t>
         </is>
       </c>
     </row>
@@ -3855,27 +3859,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Iheoma</t>
+          <t>Iheme</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>c/o Igwe</t>
+          <t>Ekene</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>No 3 Martins Street Victory Estate</t>
+          <t>17 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2347035304920</t>
+          <t>2348035007625</t>
         </is>
       </c>
     </row>
@@ -3885,27 +3889,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ijamakinwa</t>
+          <t>Iheoma</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Olabode</t>
+          <t>c/o Igwe</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2 Jibewa Shomorin Close</t>
+          <t>3 Martins Street</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2347032701075</t>
+          <t>2347035304920</t>
         </is>
       </c>
     </row>
@@ -3920,22 +3924,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ikeola</t>
+          <t>Ijamakinwa</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Rotimi</t>
+          <t>Olabode</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>No 7B Sam Ogegbo Road</t>
+          <t>2 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2348035677330</t>
+          <t>2347032701075</t>
         </is>
       </c>
     </row>
@@ -3945,27 +3949,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Iloeje</t>
+          <t>Ikeola</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Kenechukwu</t>
+          <t>Rotimi</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>10 Jibewa Shomorin Close</t>
+          <t>No 7B Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2348034960305</t>
+          <t>2348035677330</t>
         </is>
       </c>
     </row>
@@ -3975,27 +3979,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Iloeje</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Olamide </t>
+          <t>Kenechukwu</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>3 Sam Ogegbo Road</t>
+          <t>10 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348034960305</t>
         </is>
       </c>
     </row>
@@ -4005,22 +4009,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isijola </t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Olubukola</t>
+          <t xml:space="preserve"> Olamide </t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>25 Jibewa Shomorin Close</t>
+          <t>3 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4040,17 +4044,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Iya Daniel</t>
+          <t xml:space="preserve">Isijola </t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Olubukola</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>25 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4070,7 +4074,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Iya Pelumi</t>
+          <t>Iya Daniel</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4095,27 +4099,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Jaywon</t>
+          <t>Iya Pelumi</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>18 Sam Ogegbo Road</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2349068400154</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4125,27 +4129,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ms.</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Jaywon</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Ginka</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2 Jibewa Shomorin Close</t>
+          <t>18 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2348089953097</t>
+          <t>2349068400154</t>
         </is>
       </c>
     </row>
@@ -4155,27 +4159,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Ms.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Jesutobi</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Ginka</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>23 Sam Ogegbo Road</t>
+          <t>2 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2348057387415</t>
+          <t>2348089953097</t>
         </is>
       </c>
     </row>
@@ -4185,27 +4189,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Jimoh</t>
+          <t>Jesutobi</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Koulete</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2349132223243</t>
+          <t>2348057387415</t>
         </is>
       </c>
     </row>
@@ -4225,17 +4229,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Abiodun</t>
+          <t>Koulete</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>9 Victorious Avenue</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2348143798069</t>
+          <t>2349132223243</t>
         </is>
       </c>
     </row>
@@ -4250,22 +4254,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joel </t>
+          <t>Jimoh</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Ogboji</t>
+          <t>Abiodun</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1 Sam Ogegbo Road</t>
+          <t>9 Victorious Avenue</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2349065571043</t>
+          <t>2348143798069</t>
         </is>
       </c>
     </row>
@@ -4280,22 +4284,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>John</t>
+          <t xml:space="preserve">Joel </t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Ogboji</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>6 Martins Street</t>
+          <t>1 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2349065571043</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4324,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>6 Martins Street</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4340,22 +4344,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>John</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Obinna</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>13 Sam Ogegbo Road</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2348137343312</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4375,17 +4379,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Obinna</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>13 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348137343312</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4414,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>6 Martins Street</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4430,7 +4434,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Kayode</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4440,7 +4444,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>6 Martins Street</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -4460,22 +4464,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Kayode</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Olanbiwonninum</t>
+          <t>Opeyemi</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>6 Martins Street</t>
+          <t>3 Victorious Avenue</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2348130853892</t>
+          <t>2348033869066</t>
         </is>
       </c>
     </row>
@@ -4485,27 +4489,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mrs </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kemi</t>
+          <t>Kayode</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Olanbiwonninum</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>25 Jibewa Shomorin Close</t>
+          <t>6 Martins Street</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348130853892</t>
         </is>
       </c>
     </row>
@@ -4515,12 +4519,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t xml:space="preserve">Mrs </t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Kenneth</t>
+          <t>Kemi</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4530,7 +4534,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>7 Martins Street</t>
+          <t>25 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4545,12 +4549,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Korede</t>
+          <t>Kenneth</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4560,7 +4564,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>7 Martins Street</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -4580,22 +4584,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Kougnaglo</t>
+          <t>Korede</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Bartholomew</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>16 Sam Ogegbo Road</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2348034256298</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4610,22 +4614,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Lawal</t>
+          <t>Kougnaglo</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Adedolapo</t>
+          <t>Bartholomew</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>11 Jibewa Shomorin Close</t>
+          <t>16 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2347063861766</t>
+          <t>2348034256298</t>
         </is>
       </c>
     </row>
@@ -4635,27 +4639,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lawal </t>
+          <t>Lawal</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Halima</t>
+          <t>Adedolapo</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1 Adeogun Street</t>
+          <t>11 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2347063861766</t>
         </is>
       </c>
     </row>
@@ -4665,27 +4669,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Love</t>
+          <t xml:space="preserve">Lawal </t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Treasure </t>
+          <t>Halima</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>6 Olanpejo Street</t>
+          <t>1 Adeogun Street</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2348057105540</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4700,22 +4704,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makyeni </t>
+          <t>Love</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anthony </t>
+          <t xml:space="preserve"> Treasure </t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>5 Martins Street</t>
+          <t>6 Olanpejo Street</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2348130779792</t>
+          <t>2348057105540</t>
         </is>
       </c>
     </row>
@@ -4725,27 +4729,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mama </t>
+          <t xml:space="preserve">Makyeni </t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Ibo</t>
+          <t xml:space="preserve">Anthony </t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>6 Martins Street</t>
+          <t>5 Martins Street</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348130779792</t>
         </is>
       </c>
     </row>
@@ -4755,27 +4759,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mattew</t>
+          <t xml:space="preserve">Mama </t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Ibo</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>23B Jibewa Shomorin Close</t>
+          <t>6 Martins Street</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2348032019300</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4924,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3 Sam Ogegbo Street Victory estate</t>
+          <t>3 Sam Ogegbo Street</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5055,7 +5059,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5065,7 +5069,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Chiboka</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5075,7 +5079,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2348167115656</t>
+          <t>2348038222999</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5089,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5095,7 +5099,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Chiboka</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5105,7 +5109,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2348038222999</t>
+          <t>2348167115656</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5239,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ms</t>
+          <t xml:space="preserve">Ms </t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5250,12 +5254,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>22 Sam Ogegbo Road</t>
+          <t>14 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2347035566619</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5269,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ms </t>
+          <t>Ms</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5280,12 +5284,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>14 Sam Ogegbo Road</t>
+          <t>22 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2347035566619</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5299,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5305,7 +5309,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Kelechi</t>
+          <t>Franka</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5315,7 +5319,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2348033623568</t>
+          <t>2348035276474</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5329,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5335,7 +5339,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Franka</t>
+          <t>Kelechi</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5345,7 +5349,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2348035276474</t>
+          <t>2348033623568</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5459,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tunde</t>
+          <t>Gbenga</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5465,7 +5469,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2348032400317</t>
+          <t>2348172518406</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5489,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Gbenga</t>
+          <t>Tunde</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5495,7 +5499,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2348172518406</t>
+          <t>2348032400317</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5689,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5695,17 +5699,17 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Otunba</t>
+          <t>Sakirat</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>17 Jibewa Shomorin Close</t>
+          <t>6 Martins Street</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2348182300274</t>
+          <t>2349124065368</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5719,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5725,17 +5729,17 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Sakirat</t>
+          <t>Otunba</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>6 Martins Street</t>
+          <t>17 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2349124065368</t>
+          <t>2348182300274</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5809,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5815,17 +5819,17 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Ifeoluwa</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>10 Martins Street</t>
+          <t>10 Martins Street Victory estate</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2348034102329</t>
+          <t>08050511360</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5839,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5845,17 +5849,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Ifeoluwa</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>10 Martins Street Victory estate</t>
+          <t>10 Martins Street</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>08050511360</t>
+          <t>2348034102329</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6334,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>No19A Jibewa Shomorin CloseVictory Estate</t>
+          <t>19A Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7040,22 +7044,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Soji</t>
+          <t>Sola</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Adeogun</t>
+          <t>Folowosele</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>No7 Olanpejo Street Victory Estate</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2348158941240</t>
+          <t>234</t>
         </is>
       </c>
     </row>
@@ -7070,22 +7074,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Solomon</t>
+          <t>Sola</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Folowosele</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2 Adeogun Street</t>
+          <t>No7 Olanpejo Street Victory Estate</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -7100,22 +7104,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solomon </t>
+          <t>Sola</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wuike </t>
+          <t>Folowosele</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>7 Martins Street</t>
+          <t>No7 Olanpejo Street Victory Estate</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2348060221829</t>
+          <t>+234 8034102329</t>
         </is>
       </c>
     </row>
@@ -7130,17 +7134,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sunday </t>
+          <t>Solomon</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Alfred</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>9 Martins Street</t>
+          <t>2 Adeogun Street</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -7155,27 +7159,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Tajudeen</t>
+          <t xml:space="preserve">Solomon </t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Adebayo</t>
+          <t xml:space="preserve">Wuike </t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>6 Jibewa Shomorin Close</t>
+          <t>7 Martins Street</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2348023181917</t>
+          <t>2348060221829</t>
         </is>
       </c>
     </row>
@@ -7185,27 +7189,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Tokunboh</t>
+          <t xml:space="preserve">Sunday </t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Daniju</t>
+          <t>Alfred</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>3 Olanpejo Street</t>
+          <t>9 Martins Street</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2348068687060</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7220,22 +7224,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tolulope </t>
+          <t>Tajudeen</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Akinjise2</t>
+          <t>Ojo</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>23 Sam Ogegbo Road</t>
+          <t>6 Jibewa Shomorin Close</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2347033161402</t>
+          <t>2348023181917</t>
         </is>
       </c>
     </row>
@@ -7250,22 +7254,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tolulope </t>
+          <t>Talabi</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Akinjise</t>
+          <t>Yinka</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>23 Sam Ogegbo Road</t>
+          <t>7 Martins Street</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2348169696476</t>
+          <t>2348034709952</t>
         </is>
       </c>
     </row>
@@ -7275,27 +7279,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Tomisin</t>
+          <t>Tokunboh</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Obakpolo</t>
+          <t>Daniju</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>7 Martins Street</t>
+          <t>3 Olanpejo Street</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2349084860718</t>
+          <t>2348068687060</t>
         </is>
       </c>
     </row>
@@ -7305,27 +7309,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ufele</t>
+          <t xml:space="preserve">Tolulope </t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Tochukwu</t>
+          <t>Akinjise2</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>20 Sam Ogegbo Road</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2348036912727</t>
+          <t>2347033161402</t>
         </is>
       </c>
     </row>
@@ -7335,27 +7339,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Ukaha</t>
+          <t xml:space="preserve">Tolulope </t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Eberechi</t>
+          <t>Akinjise</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>16 Sam Ogegbo Road</t>
+          <t>23 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2348064383418</t>
+          <t>2348169696476</t>
         </is>
       </c>
     </row>
@@ -7365,27 +7369,27 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t xml:space="preserve">Mr </t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Ututu</t>
+          <t>Tomisin</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Cletus</t>
+          <t>Obakpolo</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>8 Sam Ogegbo Road</t>
+          <t>7 Martins Street</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2348039727477</t>
+          <t>2349084860718</t>
         </is>
       </c>
     </row>
@@ -7400,22 +7404,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Uzoma</t>
+          <t>Ufele</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Rachael</t>
+          <t>Tochukwu</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>17 Sam Ogegbo Road</t>
+          <t>20 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2347083475377</t>
+          <t>2348036912727</t>
         </is>
       </c>
     </row>
@@ -7425,27 +7429,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Engrn</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Wabara</t>
+          <t>Ugo</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Chinedu</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>5 Victorious Avenue</t>
+          <t>20 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2348188276133</t>
+          <t>2347064681113</t>
         </is>
       </c>
     </row>
@@ -7455,27 +7459,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wale </t>
+          <t>Ukaha</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Akinwunmi</t>
+          <t>Eberechi</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>8 Sam Ogegbo Road</t>
+          <t>16 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2349098037363</t>
+          <t>2348064383418</t>
         </is>
       </c>
     </row>
@@ -7485,27 +7489,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Winners </t>
+          <t>Uzoma</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Chapel</t>
+          <t>Rachael</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2 Martins Street</t>
+          <t>17 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2347083475377</t>
         </is>
       </c>
     </row>
@@ -7515,27 +7519,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Mrs</t>
+          <t>Engrn</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Wumi</t>
+          <t>Wabara</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Chinedu</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>7 Martins Street</t>
+          <t>5 Victorious Avenue</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2348188276133</t>
         </is>
       </c>
     </row>
@@ -7545,27 +7549,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mr </t>
+          <t>Mr</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Yakubu</t>
+          <t xml:space="preserve">Wale </t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>na</t>
+          <t>Akinwunmi</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2 Sam Ogegbo Road</t>
+          <t>8 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2349032219116</t>
+          <t>2349098037363</t>
         </is>
       </c>
     </row>
@@ -7580,22 +7584,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yesua </t>
+          <t xml:space="preserve">Winners </t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Chapel</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>22 Jibewa Shomorin Close</t>
+          <t>2 Martins Street</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2348133398748</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7605,27 +7609,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Mr</t>
+          <t>Mrs</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Yetunde</t>
+          <t>Wumi</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Ikeola</t>
+          <t>na</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>7B Sam Ogegbo Road</t>
+          <t>7 Martins Street</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2348027967022</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7644,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Yinka</t>
+          <t>Yakubu</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -7650,12 +7654,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>7 Martins Street</t>
+          <t>2 Sam Ogegbo Road</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2348034709952</t>
+          <t>2349032219116</t>
         </is>
       </c>
     </row>
@@ -7670,20 +7674,80 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
+          <t xml:space="preserve">Yesua </t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>School</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>22 Jibewa Shomorin Close</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2348133398748</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Yetunde</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Ikeola</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>7B Sam Ogegbo Road</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2348027967022</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Mr</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
           <t>Young</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>Kelly</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E244" t="inlineStr">
         <is>
           <t>3 Victorious Avenue</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
+      <c r="F244" t="inlineStr">
         <is>
           <t>0</t>
         </is>
